--- a/jogos_2024-12-18.xlsx
+++ b/jogos_2024-12-18.xlsx
@@ -1665,7 +1665,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1675,16 +1675,16 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Clodiense</t>
+          <t>Valencia W</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Calcio Padova</t>
+          <t>Deportivo de La Coruña W</t>
         </is>
       </c>
       <c r="G10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H10" t="n">
         <v>2</v>
@@ -1693,7 +1693,7 @@
         <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
@@ -1701,83 +1701,83 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>7</v>
+        <v>2.15</v>
       </c>
       <c r="M10" t="n">
-        <v>3.5</v>
+        <v>3.1</v>
       </c>
       <c r="N10" t="n">
-        <v>1.48</v>
+        <v>3</v>
       </c>
       <c r="O10" t="n">
-        <v>7</v>
+        <v>2.88</v>
       </c>
       <c r="P10" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.05</v>
+        <v>3.75</v>
       </c>
       <c r="R10" t="n">
-        <v>1.4</v>
+        <v>1.45</v>
       </c>
       <c r="S10" t="n">
-        <v>2.75</v>
+        <v>2.55</v>
       </c>
       <c r="T10" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="U10" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="V10" t="n">
         <v>1.05</v>
       </c>
       <c r="W10" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="X10" t="n">
-        <v>3</v>
+        <v>2.95</v>
       </c>
       <c r="Y10" t="n">
-        <v>2.15</v>
+        <v>2.05</v>
       </c>
       <c r="Z10" t="n">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="AA10" t="n">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="AC10" t="n">
-        <v>2.25</v>
+        <v>1.8</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.57</v>
+        <v>1.83</v>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>['90+4']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>['32', '55']</t>
+          <t>['55', '90+4']</t>
         </is>
       </c>
       <c r="AG10" t="n">
-        <v>2.04</v>
+        <v>1.29</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.11</v>
+        <v>1.51</v>
       </c>
       <c r="AI10" t="n">
-        <v>4</v>
+        <v>1.85</v>
       </c>
       <c r="AJ10" t="n">
-        <v>1.33</v>
+        <v>2.3</v>
       </c>
       <c r="AK10" s="3" t="n">
         <v>45644.6875</v>
@@ -1794,7 +1794,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1804,16 +1804,16 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Valencia W</t>
+          <t>Clodiense</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Deportivo de La Coruña W</t>
+          <t>Calcio Padova</t>
         </is>
       </c>
       <c r="G11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H11" t="n">
         <v>2</v>
@@ -1822,7 +1822,7 @@
         <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
@@ -1830,83 +1830,83 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>2.15</v>
+        <v>7</v>
       </c>
       <c r="M11" t="n">
-        <v>3.1</v>
+        <v>3.5</v>
       </c>
       <c r="N11" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="O11" t="n">
+        <v>7</v>
+      </c>
+      <c r="P11" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="R11" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S11" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="T11" t="n">
         <v>3</v>
       </c>
-      <c r="O11" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="P11" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="R11" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="S11" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="T11" t="n">
-        <v>3.1</v>
-      </c>
       <c r="U11" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="V11" t="n">
         <v>1.05</v>
       </c>
       <c r="W11" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="X11" t="n">
-        <v>2.95</v>
+        <v>3</v>
       </c>
       <c r="Y11" t="n">
-        <v>2.05</v>
+        <v>2.15</v>
       </c>
       <c r="Z11" t="n">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="AA11" t="n">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="AC11" t="n">
-        <v>1.8</v>
+        <v>2.25</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.83</v>
+        <v>1.57</v>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['90+4']</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>['55', '90+4']</t>
+          <t>['32', '55']</t>
         </is>
       </c>
       <c r="AG11" t="n">
-        <v>1.29</v>
+        <v>2.04</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.51</v>
+        <v>1.11</v>
       </c>
       <c r="AI11" t="n">
-        <v>1.85</v>
+        <v>4</v>
       </c>
       <c r="AJ11" t="n">
-        <v>2.3</v>
+        <v>1.33</v>
       </c>
       <c r="AK11" s="3" t="n">
         <v>45644.6875</v>
